--- a/docs/gara-appalto/GAP-ANALYSIS-GESTIONALE-MIO-NEGOZIO.xlsx
+++ b/docs/gara-appalto/GAP-ANALYSIS-GESTIONALE-MIO-NEGOZIO.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Gap Analysis" sheetId="1" r:id="rId1"/>
     <sheet name="Gap Critici" sheetId="2" r:id="rId2"/>
+    <sheet name="Valore Aggiunto" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -399,16 +400,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H67"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="35.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1876,13 +1867,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E12"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2059,4 +2043,721 @@
     <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D64"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>VALORE AGGIUNTO W3SUITE - Capacità Distintive</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>#</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Funzionalità</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Tecnologia</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Benefici WindTre</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>AGENTI AI RAGGIUNGIBILI</v>
+      </c>
+      <c r="C5" t="str">
+        <v>AI Voice Agent + RAG</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>- Assistente vocale AI 24/7</v>
+      </c>
+      <c r="C6" t="str">
+        <v>OpenAI GPT-4 + RAG</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Riduzione carico call center 40-60%</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v>- Context-aware (cliente, ordini, storico)</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Knowledge Base dinamica</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Risposta immediata h24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>- Handoff automatico a operatore umano</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Intelligent Routing</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Standardizzazione qualità supporto</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v>- Multi-lingua italiano/inglese</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MCP GATEWAY</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Multi-Channel Provider Gateway</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v>- Single Point of Integration</v>
+      </c>
+      <c r="C12" t="str">
+        <v>API Gateway unificato</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Integrazione semplificata sistemi WindTre</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v>- Provider: OpenAI, Twilio, WhatsApp, SMS</v>
+      </c>
+      <c r="C13" t="str">
+        <v>OAuth2/OIDC</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Riduzione tempi sviluppo 70%</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v>- Fallback automatico tra provider</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Rate Limiting granulare</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Governance centralizzata accessi API</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <v>- Audit completo tutte interazioni</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3</v>
+      </c>
+      <c r="B17" t="str">
+        <v>UNIVERSAL WORKFLOW ENGINE</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Visual Builder + AI</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <v>- Drag-and-drop senza codice</v>
+      </c>
+      <c r="C18" t="str">
+        <v>AI Workflow Builder</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Time-to-market: settimane → ore</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <v>- Intelligent Routing (regole, turni, competenze)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Trigger multipli</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Standardizzazione processi rete</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <v>- Cross-store workflows</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Template library</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Adattabilità rapida nuove esigenze</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v>- Versioning con rollback</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>4</v>
+      </c>
+      <c r="B23" t="str">
+        <v>SISTEMA CHIAMATE WebRTC</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Browser-based real-time</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <v>- Click-to-call dal CRM</v>
+      </c>
+      <c r="C24" t="str">
+        <v>WebRTC + SIP</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Eliminazione costi licenze softphone</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
+      </c>
+      <c r="B25" t="str">
+        <v>- Softphone integrato nel browser</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Recording + Trascrizione AI</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Integrazione nativa CRM</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <v>- Whisper mode / Barge-in supervisor</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Video call + Screen sharing</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Analytics chiamate</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <v>- IVR dinamico configurabile</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>5</v>
+      </c>
+      <c r="B29" t="str">
+        <v>AI ENFORCEMENT MIDDLEWARE</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Quality Assurance Layer</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <v>- Content moderation automatica</v>
+      </c>
+      <c r="C30" t="str">
+        <v>AI Policy Enforcement</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Riduzione rischio compliance</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v/>
+      </c>
+      <c r="B31" t="str">
+        <v>- Compliance check AGCOM/privacy</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Quality scoring real-time</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Miglioramento qualità +15%</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v/>
+      </c>
+      <c r="B32" t="str">
+        <v>- Anomaly detection frodi</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Suggestion engine</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Early warning problematiche</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>6</v>
+      </c>
+      <c r="B34" t="str">
+        <v>ANALYTICS AI-POWERED</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Predictive BI</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
+      </c>
+      <c r="B35" t="str">
+        <v>- Predictive analytics (vendite, churn)</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Natural language queries</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Decision-making data-driven</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v/>
+      </c>
+      <c r="B36" t="str">
+        <v>- Automated insights con trend</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Benchmark automatico</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Riduzione tempo analisi 80%</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v/>
+      </c>
+      <c r="B37" t="str">
+        <v>- What-if analysis scenari</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>7</v>
+      </c>
+      <c r="B39" t="str">
+        <v>ARCHITETTURA ENTERPRISE-GRADE</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Security &amp; Compliance</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v/>
+      </c>
+      <c r="B40" t="str">
+        <v>- Multi-tenant nativo</v>
+      </c>
+      <c r="C40" t="str">
+        <v>PostgreSQL RLS</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Isolamento completo dealer</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
+        <v>- 3-level RBAC</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Zero-trust</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Controllo accessi granulare</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+      <c r="B42" t="str">
+        <v>- Audit immutabile (event sourcing)</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Encryption AES-256/TLS 1.3</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Tracciabilità completa</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>CONFRONTO COMPETITIVO</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Funzionalità</v>
+      </c>
+      <c r="B47" t="str">
+        <v>W3Suite</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Competitor A</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Competitor B</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>AI Voice Agent</v>
+      </c>
+      <c r="B48" t="str">
+        <v>NATIVO</v>
+      </c>
+      <c r="C48" t="str">
+        <v>NO</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Add-on</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>MCP Gateway</v>
+      </c>
+      <c r="B49" t="str">
+        <v>NATIVO</v>
+      </c>
+      <c r="C49" t="str">
+        <v>NO</v>
+      </c>
+      <c r="D49" t="str">
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Workflow AI Builder</v>
+      </c>
+      <c r="B50" t="str">
+        <v>NATIVO</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Basic</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Basic</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>WebRTC Calls</v>
+      </c>
+      <c r="B51" t="str">
+        <v>NATIVO</v>
+      </c>
+      <c r="C51" t="str">
+        <v>NO</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Add-on</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>AI Enforcement</v>
+      </c>
+      <c r="B52" t="str">
+        <v>NATIVO</v>
+      </c>
+      <c r="C52" t="str">
+        <v>NO</v>
+      </c>
+      <c r="D52" t="str">
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Predictive Analytics</v>
+      </c>
+      <c r="B53" t="str">
+        <v>NATIVO</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Basic</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Basic</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Multi-tenant RLS</v>
+      </c>
+      <c r="B54" t="str">
+        <v>NATIVO</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Parziale</v>
+      </c>
+      <c r="D54" t="str">
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>ROI STIMATO VALORE AGGIUNTO</v>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Funzionalità</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Risparmio/Beneficio Annuo</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>AI Voice Agent 24/7</v>
+      </c>
+      <c r="B60" t="str">
+        <v>-40% costi call center</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Workflow automation</v>
+      </c>
+      <c r="B61" t="str">
+        <v>-60% tempo gestione processi</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>WebRTC integrato</v>
+      </c>
+      <c r="B62" t="str">
+        <v>-100% licenze softphone</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>AI Quality scoring</v>
+      </c>
+      <c r="B63" t="str">
+        <v>+15% customer satisfaction</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Predictive analytics</v>
+      </c>
+      <c r="B64" t="str">
+        <v>+10% vendite (ottimizzazione stock)</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D64"/>
+  </ignoredErrors>
+</worksheet>
 </file>